--- a/data/trans_camb/P0902-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,47</t>
+          <t>1,05; 7,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,89</t>
+          <t>0,63; 7,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,94</t>
+          <t>3,54; 9,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 14,28</t>
+          <t>6,39; 14,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 15,87</t>
+          <t>8,13; 15,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 11,74</t>
+          <t>5,5; 12,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 10,02</t>
+          <t>4,92; 10,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 10,43</t>
+          <t>5,59; 10,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 10,41</t>
+          <t>5,59; 10,41</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 122,7</t>
+          <t>11,21; 123,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 107,32</t>
+          <t>6,59; 111,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,48; 151,69</t>
+          <t>37,56; 157,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,61; 158,67</t>
+          <t>49,77; 159,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,82; 178,7</t>
+          <t>66,01; 181,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,11; 134,61</t>
+          <t>44,01; 139,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,75; 124,85</t>
+          <t>49,58; 129,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,04; 130,13</t>
+          <t>53,24; 131,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,6; 130,49</t>
+          <t>53,33; 130,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,57</t>
+          <t>1,01; 6,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,36</t>
+          <t>-1,82; 3,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,14</t>
+          <t>-4,31; 4,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 11,95</t>
+          <t>5,19; 11,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 6,36</t>
+          <t>-0,04; 6,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,14</t>
+          <t>3,03; 9,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,47</t>
+          <t>4,0; 8,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,09</t>
+          <t>0,02; 4,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,46</t>
+          <t>-2,08; 5,49</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 96,65</t>
+          <t>10,29; 96,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 47,79</t>
+          <t>-18,84; 46,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 55,29</t>
+          <t>-40,82; 58,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,94; 102,12</t>
+          <t>33,27; 99,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 53,27</t>
+          <t>-1,04; 55,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 76,62</t>
+          <t>19,13; 81,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,24; 86,03</t>
+          <t>34,19; 88,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 41,16</t>
+          <t>0,1; 43,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 53,4</t>
+          <t>-19,02; 54,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 3,23</t>
+          <t>-2,99; 3,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1,37</t>
+          <t>-4,36; 1,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,46</t>
+          <t>1,54; 8,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,61</t>
+          <t>-3,06; 4,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 3,49</t>
+          <t>-4,33; 3,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 2,47</t>
+          <t>-10,86; 2,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,82</t>
+          <t>-2,11; 2,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,36</t>
+          <t>-3,43; 1,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 4,35</t>
+          <t>-3,82; 4,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,23; 46,16</t>
+          <t>-30,06; 43,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,53; 18,51</t>
+          <t>-42,28; 18,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,23; 114,57</t>
+          <t>13,87; 117,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 31,68</t>
+          <t>-16,82; 30,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 23,49</t>
+          <t>-24,03; 23,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,14; 15,46</t>
+          <t>-57,19; 16,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 25,03</t>
+          <t>-15,25; 23,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 11,64</t>
+          <t>-24,93; 14,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,51; 36,83</t>
+          <t>-26,6; 36,32</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,7</t>
+          <t>0,32; 5,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,0</t>
+          <t>-1,07; 4,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,74</t>
+          <t>1,57; 6,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,42</t>
+          <t>-1,0; 5,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,44</t>
+          <t>-3,44; 3,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,0</t>
+          <t>-1,88; 6,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,54</t>
+          <t>0,51; 4,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,0</t>
+          <t>-1,41; 2,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,74</t>
+          <t>1,3; 5,84</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,74; 82,34</t>
+          <t>3,0; 89,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 58,96</t>
+          <t>-12,12; 60,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,46; 97,68</t>
+          <t>17,68; 100,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 36,44</t>
+          <t>-5,45; 36,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 22,12</t>
+          <t>-18,74; 21,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 39,0</t>
+          <t>-10,05; 41,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 40,54</t>
+          <t>3,56; 38,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 25,11</t>
+          <t>-10,21; 23,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,84; 49,92</t>
+          <t>9,8; 50,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,35</t>
+          <t>1,35; 4,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,43</t>
+          <t>-0,31; 2,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,4</t>
+          <t>0,85; 5,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,11</t>
+          <t>3,54; 7,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,93</t>
+          <t>1,48; 5,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 5,58</t>
+          <t>0,12; 5,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,33</t>
+          <t>3,03; 5,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,26</t>
+          <t>1,02; 3,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,05</t>
+          <t>1,76; 5,26</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>16,59; 58,76</t>
+          <t>15,22; 59,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 32,78</t>
+          <t>-3,55; 35,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15,05; 71,21</t>
+          <t>13,07; 72,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,56; 52,01</t>
+          <t>23,16; 52,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,47; 35,94</t>
+          <t>9,78; 36,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,66; 39,64</t>
+          <t>2,46; 40,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,65; 48,13</t>
+          <t>24,98; 48,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7,96; 30,04</t>
+          <t>8,42; 30,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,69; 45,96</t>
+          <t>15,65; 48,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0902-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Habitat-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,81</t>
+          <t>8,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>7,65</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,73</t>
+          <t>1,29; 7,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,01</t>
+          <t>0,58; 6,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,89</t>
+          <t>2,92; 9,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 14,35</t>
+          <t>6,68; 14,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 15,99</t>
+          <t>7,96; 16,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 12,21</t>
+          <t>5,53; 11,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 10,16</t>
+          <t>4,92; 9,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,82</t>
+          <t>5,28; 10,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,41</t>
+          <t>5,29; 10,07</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 123,34</t>
+          <t>14,06; 116,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 111,1</t>
+          <t>6,57; 105,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,56; 157,09</t>
+          <t>30,66; 150,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,77; 159,9</t>
+          <t>51,59; 157,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,01; 181,02</t>
+          <t>67,62; 182,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,01; 139,54</t>
+          <t>44,5; 135,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,58; 129,37</t>
+          <t>48,83; 127,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,24; 131,91</t>
+          <t>51,99; 131,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,33; 130,01</t>
+          <t>51,3; 128,19</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>4,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,44</t>
+          <t>0,89; 6,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,27</t>
+          <t>-1,34; 3,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 4,3</t>
+          <t>0,58; 5,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,99</t>
+          <t>5,14; 11,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,9</t>
+          <t>-0,34; 6,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,52</t>
+          <t>2,88; 9,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,48</t>
+          <t>3,97; 8,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,24</t>
+          <t>-0,25; 4,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 5,49</t>
+          <t>2,48; 6,57</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,29; 96,92</t>
+          <t>9,95; 93,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 46,57</t>
+          <t>-15,15; 52,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 58,81</t>
+          <t>5,7; 84,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,27; 99,52</t>
+          <t>33,4; 99,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 55,85</t>
+          <t>-2,39; 53,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,13; 81,79</t>
+          <t>18,37; 73,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,19; 88,25</t>
+          <t>32,16; 85,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 43,87</t>
+          <t>-2,09; 41,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 54,0</t>
+          <t>20,71; 66,58</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>3,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 3,23</t>
+          <t>-3,19; 2,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,27</t>
+          <t>-4,65; 1,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,47</t>
+          <t>0,98; 7,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 4,66</t>
+          <t>-3,19; 4,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 3,58</t>
+          <t>-4,38; 3,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 2,65</t>
+          <t>-1,13; 6,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,74</t>
+          <t>-2,09; 3,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,68</t>
+          <t>-3,69; 1,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,44</t>
+          <t>0,96; 5,98</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-15,6%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 43,75</t>
+          <t>-31,34; 41,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,28; 18,37</t>
+          <t>-43,65; 20,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,87; 117,0</t>
+          <t>8,37; 105,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 30,76</t>
+          <t>-17,35; 31,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 23,54</t>
+          <t>-22,82; 24,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 16,55</t>
+          <t>-6,36; 40,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 23,87</t>
+          <t>-14,63; 26,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 14,5</t>
+          <t>-26,11; 15,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 36,32</t>
+          <t>6,63; 52,7</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>3,71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>3,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,95</t>
+          <t>0,31; 5,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,11</t>
+          <t>-1,09; 4,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,71</t>
+          <t>1,43; 6,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,59</t>
+          <t>-1,23; 5,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 3,23</t>
+          <t>-3,54; 3,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 6,38</t>
+          <t>0,59; 7,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,62</t>
+          <t>0,3; 4,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,65</t>
+          <t>-1,49; 2,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,84</t>
+          <t>1,84; 5,93</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,0; 89,44</t>
+          <t>1,28; 83,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 60,45</t>
+          <t>-12,62; 62,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,68; 100,68</t>
+          <t>16,67; 97,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 36,34</t>
+          <t>-6,33; 34,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 21,18</t>
+          <t>-18,94; 22,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 41,24</t>
+          <t>3,61; 46,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,56; 38,61</t>
+          <t>2,07; 40,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 23,09</t>
+          <t>-11,1; 24,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,8; 50,81</t>
+          <t>13,14; 50,08</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>4,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,5</t>
+          <t>1,44; 4,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,66</t>
+          <t>-0,26; 2,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,45</t>
+          <t>2,83; 5,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,2</t>
+          <t>3,38; 7,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,04</t>
+          <t>1,27; 4,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,57</t>
+          <t>3,38; 6,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,24</t>
+          <t>2,93; 5,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,32</t>
+          <t>1,01; 3,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,26</t>
+          <t>3,61; 5,83</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15,22; 59,45</t>
+          <t>15,92; 55,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 35,13</t>
+          <t>-2,93; 31,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13,07; 72,01</t>
+          <t>32,01; 76,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,16; 52,19</t>
+          <t>21,89; 51,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,78; 36,37</t>
+          <t>7,98; 36,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,46; 40,78</t>
+          <t>21,64; 47,85</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,98; 48,38</t>
+          <t>24,18; 48,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,42; 30,88</t>
+          <t>7,97; 30,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,65; 48,38</t>
+          <t>30,11; 53,65</t>
         </is>
       </c>
     </row>
